--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,234 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129880600</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grindstugan, Grindstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607751</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6521148</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bärbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129880599</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grindstugan, Grindstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607743</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6521073</v>
+      </c>
+      <c r="S4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bärbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92957</v>
+        <v>92959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129872267</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129880600</v>
       </c>
       <c r="B3" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129880599</v>
       </c>
       <c r="B4" t="n">
-        <v>92959</v>
+        <v>93046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58288-2025 artfynd.xlsx
+++ b/artfynd/A 58288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129872267</v>
+        <v>129880598</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grindstugan, Grindstugan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607732</v>
+        <v>607751</v>
       </c>
       <c r="R2" t="n">
-        <v>6521061</v>
+        <v>6521044</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129880600</v>
+        <v>129880599</v>
       </c>
       <c r="B3" t="n">
-        <v>92961</v>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607751</v>
+        <v>607743</v>
       </c>
       <c r="R3" t="n">
-        <v>6521148</v>
+        <v>6521073</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,55 +899,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129880599</v>
+        <v>129872267</v>
       </c>
       <c r="B4" t="n">
-        <v>92959</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grindstugan, Grindstugan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607743</v>
+        <v>607732</v>
       </c>
       <c r="R4" t="n">
-        <v>6521073</v>
+        <v>6521061</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,22 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,6 +1003,120 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129880600</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grindstugan, Grindstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607751</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521148</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bärbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
